--- a/src/flychams_common/config/Configuration-JJAA.xlsx
+++ b/src/flychams_common/config/Configuration-JJAA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -64,57 +64,57 @@
     <t xml:space="preserve">StartHour</t>
   </si>
   <si>
+    <t xml:space="preserve">MISSION00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Multi-Camera Agents Configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENVIRONMENT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-150.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(30.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13/12/2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16:30:00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Multi-Camera Agents Configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Multi-Camera Agents Configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM02</t>
+  </si>
+  <si>
     <t xml:space="preserve">X</t>
   </si>
   <si>
-    <t xml:space="preserve">MISSION00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Multi-Camera Agents Configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENVIRONMENT00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-150.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(30.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13/12/2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(16:30:00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Multi-Camera Agents Configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Multi-Camera Agents Configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM02</t>
-  </si>
-  <si>
     <t xml:space="preserve">MISSION03</t>
   </si>
   <si>
@@ -460,7 +460,7 @@
     <t xml:space="preserve">Central</t>
   </si>
   <si>
-    <t xml:space="preserve">(X=0.0, Y=0.0, Z=-0.05)</t>
+    <t xml:space="preserve">(X=0.0, Y=0.0, Z=-0.08)</t>
   </si>
   <si>
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=90.0)</t>
@@ -481,7 +481,7 @@
     <t xml:space="preserve">Tracking</t>
   </si>
   <si>
-    <t xml:space="preserve">(X=0.3, Y=0.0, Z=-0.05)</t>
+    <t xml:space="preserve">(X=0.19, Y=0.0, Z=-0.04)</t>
   </si>
   <si>
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=0.0)</t>
@@ -496,7 +496,7 @@
     <t xml:space="preserve">Tracking Multi-Camera 1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">(X=0.0, Y=0.3, Z=-0.05)</t>
+    <t xml:space="preserve">(X=-0.19, Y=0.0, Z=-0.04)</t>
   </si>
   <si>
     <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT00/MULTICAMERA02</t>
@@ -1007,18 +1007,18 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="2" tint="-0.75"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="2" tint="-0.75"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1145,7 +1145,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1157,7 +1157,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1165,7 +1165,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1754,38 +1754,36 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -1834,36 +1832,36 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>24</v>
-      </c>
       <c r="G4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -1912,36 +1910,36 @@
       <c r="BD4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="G5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
@@ -1990,7 +1988,9 @@
       <c r="BD5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13"/>
+      <c r="A6" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
@@ -1998,28 +1998,28 @@
         <v>29</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
@@ -2068,7 +2068,7 @@
       <c r="BD6" s="12"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="9" t="s">
         <v>31</v>
       </c>
@@ -2076,28 +2076,28 @@
         <v>32</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="I7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="J7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="K7" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
@@ -2146,7 +2146,7 @@
       <c r="BD7" s="12"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="9" t="s">
         <v>34</v>
       </c>
@@ -2154,28 +2154,28 @@
         <v>35</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="I8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="J8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="K8" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>39</v>
@@ -2592,7 +2592,7 @@
         <v>50</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>51</v>
@@ -2776,7 +2776,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>64</v>
@@ -2799,7 +2799,6 @@
       <c r="J3" s="19" t="n">
         <v>12000</v>
       </c>
-      <c r="XFD3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
@@ -2809,7 +2808,7 @@
         <v>69</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>70</v>
@@ -2832,7 +2831,6 @@
       <c r="J4" s="19" t="n">
         <v>12000</v>
       </c>
-      <c r="XFD4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
@@ -2842,7 +2840,7 @@
         <v>72</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>73</v>
@@ -2874,7 +2872,7 @@
         <v>76</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>77</v>
@@ -2897,7 +2895,6 @@
       <c r="J6" s="19" t="n">
         <v>12000</v>
       </c>
-      <c r="XFD6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
@@ -2907,7 +2904,7 @@
         <v>79</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>80</v>
@@ -2939,7 +2936,7 @@
         <v>82</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>83</v>
@@ -3463,11 +3460,11 @@
       <c r="XEW11" s="2"/>
       <c r="XEX11" s="2"/>
       <c r="XEY11" s="3"/>
-      <c r="XEZ11" s="0"/>
-      <c r="XFA11" s="0"/>
-      <c r="XFB11" s="0"/>
-      <c r="XFC11" s="0"/>
-      <c r="XFD11" s="0"/>
+      <c r="XEZ11" s="3"/>
+      <c r="XFA11" s="3"/>
+      <c r="XFB11" s="3"/>
+      <c r="XFC11" s="3"/>
+      <c r="XFD11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
@@ -3493,11 +3490,11 @@
       <c r="XEW12" s="2"/>
       <c r="XEX12" s="2"/>
       <c r="XEY12" s="3"/>
-      <c r="XEZ12" s="0"/>
-      <c r="XFA12" s="0"/>
-      <c r="XFB12" s="0"/>
-      <c r="XFC12" s="0"/>
-      <c r="XFD12" s="0"/>
+      <c r="XEZ12" s="3"/>
+      <c r="XFA12" s="3"/>
+      <c r="XFB12" s="3"/>
+      <c r="XFC12" s="3"/>
+      <c r="XFD12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
@@ -3523,11 +3520,11 @@
       <c r="XEW13" s="2"/>
       <c r="XEX13" s="2"/>
       <c r="XEY13" s="3"/>
-      <c r="XEZ13" s="0"/>
-      <c r="XFA13" s="0"/>
-      <c r="XFB13" s="0"/>
-      <c r="XFC13" s="0"/>
-      <c r="XFD13" s="0"/>
+      <c r="XEZ13" s="3"/>
+      <c r="XFA13" s="3"/>
+      <c r="XFB13" s="3"/>
+      <c r="XFC13" s="3"/>
+      <c r="XFD13" s="3"/>
     </row>
     <row r="14" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
@@ -3553,11 +3550,11 @@
       <c r="XEW14" s="2"/>
       <c r="XEX14" s="2"/>
       <c r="XEY14" s="3"/>
-      <c r="XEZ14" s="0"/>
-      <c r="XFA14" s="0"/>
-      <c r="XFB14" s="0"/>
-      <c r="XFC14" s="0"/>
-      <c r="XFD14" s="0"/>
+      <c r="XEZ14" s="3"/>
+      <c r="XFA14" s="3"/>
+      <c r="XFB14" s="3"/>
+      <c r="XFC14" s="3"/>
+      <c r="XFD14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3824,7 +3821,7 @@
       <c r="L6" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="XFD6" s="0"/>
+      <c r="XFD6" s="3"/>
     </row>
     <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
@@ -3863,7 +3860,7 @@
       <c r="L7" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="XFD7" s="0"/>
+      <c r="XFD7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
@@ -3902,7 +3899,7 @@
       <c r="L8" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="XFD8" s="0"/>
+      <c r="XFD8" s="3"/>
     </row>
     <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
@@ -3941,7 +3938,7 @@
       <c r="L9" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="XFD9" s="0"/>
+      <c r="XFD9" s="3"/>
     </row>
     <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
@@ -3980,7 +3977,7 @@
       <c r="L10" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="XFD10" s="0"/>
+      <c r="XFD10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
@@ -4019,7 +4016,7 @@
       <c r="L11" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="XFD11" s="0"/>
+      <c r="XFD11" s="3"/>
     </row>
     <row r="12" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
@@ -4058,7 +4055,7 @@
       <c r="L12" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="XFD12" s="0"/>
+      <c r="XFD12" s="3"/>
     </row>
     <row r="13" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
@@ -4097,7 +4094,7 @@
       <c r="L13" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="XFD13" s="0"/>
+      <c r="XFD13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
@@ -4136,7 +4133,7 @@
       <c r="L14" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="XFD14" s="0"/>
+      <c r="XFD14" s="3"/>
     </row>
     <row r="15" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
@@ -4175,7 +4172,7 @@
       <c r="L15" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="XFD15" s="0"/>
+      <c r="XFD15" s="3"/>
     </row>
     <row r="16" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
@@ -4214,7 +4211,7 @@
       <c r="L16" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="XFD16" s="0"/>
+      <c r="XFD16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
@@ -4253,7 +4250,7 @@
       <c r="L17" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="XFD17" s="0"/>
+      <c r="XFD17" s="3"/>
     </row>
     <row r="18" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
@@ -4292,7 +4289,7 @@
       <c r="L18" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="XFD18" s="0"/>
+      <c r="XFD18" s="3"/>
     </row>
     <row r="19" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
@@ -4331,7 +4328,7 @@
       <c r="L19" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="XFD19" s="0"/>
+      <c r="XFD19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
@@ -4370,7 +4367,7 @@
       <c r="L20" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="XFD20" s="0"/>
+      <c r="XFD20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
@@ -4392,7 +4389,7 @@
         <v>142</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H21" s="19" t="s">
         <v>144</v>
@@ -4430,7 +4427,7 @@
         <v>142</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H22" s="19" t="s">
         <v>144</v>
@@ -4468,7 +4465,7 @@
         <v>142</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H23" s="19" t="s">
         <v>144</v>
@@ -4506,7 +4503,7 @@
         <v>142</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H24" s="19" t="s">
         <v>144</v>
@@ -4544,7 +4541,7 @@
         <v>142</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H25" s="19" t="s">
         <v>144</v>
@@ -4582,7 +4579,7 @@
         <v>142</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H26" s="19" t="s">
         <v>144</v>
@@ -4725,7 +4722,6 @@
       <c r="G4" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
@@ -4772,7 +4768,6 @@
       <c r="G6" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
@@ -4819,7 +4814,6 @@
       <c r="G8" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
@@ -4866,7 +4860,6 @@
       <c r="G10" s="19" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">

--- a/src/flychams_common/config/Configuration-JJAA.xlsx
+++ b/src/flychams_common/config/Configuration-JJAA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -64,6 +64,9 @@
     <t xml:space="preserve">StartHour</t>
   </si>
   <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
     <t xml:space="preserve">MISSION00</t>
   </si>
   <si>
@@ -110,9 +113,6 @@
   </si>
   <si>
     <t xml:space="preserve">TEAM02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X</t>
   </si>
   <si>
     <t xml:space="preserve">MISSION03</t>
@@ -1007,18 +1007,18 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="2" tint="-0.75"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1145,7 +1145,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1157,7 +1157,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1165,7 +1165,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1754,36 +1754,38 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="B3" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -1834,34 +1836,34 @@
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>20</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -1910,36 +1912,36 @@
       <c r="BD4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
@@ -1988,9 +1990,7 @@
       <c r="BD5" s="12"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>27</v>
-      </c>
+      <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
@@ -1998,28 +1998,28 @@
         <v>29</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
@@ -2076,28 +2076,28 @@
         <v>32</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
@@ -2154,28 +2154,28 @@
         <v>35</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>39</v>
@@ -2592,7 +2592,7 @@
         <v>50</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>51</v>
@@ -2776,7 +2776,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>64</v>
@@ -2808,7 +2808,7 @@
         <v>69</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>70</v>
@@ -2840,7 +2840,7 @@
         <v>72</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>73</v>
@@ -2872,7 +2872,7 @@
         <v>76</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>77</v>
@@ -2904,7 +2904,7 @@
         <v>79</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>80</v>
@@ -2936,7 +2936,7 @@
         <v>82</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>83</v>
